--- a/out/07_Ops/SNX-OPS-FRM-05 Testing UAT Quality Verification (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-FRM-05 Testing UAT Quality Verification (Rev00 DRAFT).xlsx
@@ -16,8 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan dan Persetujuan" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Kasus Uji'!$A$4:$K$87</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Kasus Uji'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Defect'!$A$4:$I$45</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Defect'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -172,7 +175,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -305,6 +308,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -706,8 +733,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="3" s="24">
+      <c r="A3" s="45" t="n"/>
+      <c r="B3" s="45" t="n"/>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="24">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -717,9 +751,12 @@
           <t>SNX-OPS-FRM-05</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="24">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -729,9 +766,12 @@
           <t>Testing / UAT &amp; Quality Verification Records</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="24">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -741,9 +781,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="24">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -753,9 +796,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="C7" s="45" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="24">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -765,9 +811,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="24">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="45" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="24">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -777,9 +826,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="24">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="24">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -789,9 +841,12 @@
           <t>Project Manager</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="24">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="24">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -801,9 +856,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="24">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="24">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -813,9 +871,12 @@
           <t>Klausul 8.6, 8.7</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="24">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="24">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -825,9 +886,12 @@
           <t>Kontrol Annex A 8.29</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="24">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="C13" s="45" t="n"/>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="45" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="24">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -837,140 +901,200 @@
           <t>Durasi kontrak + 3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="24">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="24">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>Merekam rencana uji, eksekusi kasus uji, defect, dan persetujuan UAT sebagai dasar BAST (gate G2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="24">
-      <c r="A17" s="29" t="inlineStr">
+          <t>Mencatat rencana uji, eksekusi kasus uji, defect, dan persetujuan UAT sebagai dasar BAST (gate G2).</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
+    </row>
+    <row r="16" s="24">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="24">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="24">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="B17" s="45" t="n"/>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="45" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="24">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>Satu file per proyek atau per rilis; ganti nama menjadi FRM-05_&lt;KodeProyek&gt;.xlsx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="24">
-      <c r="A19" s="30" t="inlineStr">
+          <t>Gunakan satu file untuk satu proyek atau satu rilis, dengan nama FRM-05_&lt;KodeProyek&gt;.xlsx.</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="24">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>Isi Rencana Uji, lalu kasus uji dari kriteria penerimaan di project charter (SNX-OPS-FRM-01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="24">
-      <c r="A20" s="30" t="inlineStr">
+          <t>Isi Rencana Uji, lalu susun kasus uji dari kriteria penerimaan di project charter (SNX-OPS-FRM-01).</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" s="24">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>Kasus berstatus Gagal wajib punya Defect ID di sheet Defect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="23.85" customHeight="1" s="24">
-      <c r="A21" s="30" t="inlineStr">
+          <t>Setiap kasus berstatus Gagal wajib punya Defect ID di sheet Defect.</t>
+        </is>
+      </c>
+      <c r="C20" s="45" t="n"/>
+      <c r="D20" s="45" t="n"/>
+      <c r="E20" s="45" t="n"/>
+    </row>
+    <row r="21" ht="43.5" customHeight="1" s="24">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Sheet Ringkasan dan Persetujuan menghitung tingkat kelulusan dan memberi rekomendasi; UAT ditandatangani bila rekomendasinya SIAP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="24">
-      <c r="A23" s="29" t="inlineStr">
+          <t>Sheet Ringkasan dan Persetujuan menghitung tingkat kelulusan dan memberi rekomendasi. UAT ditandatangani jika rekomendasinya SIAP.</t>
+        </is>
+      </c>
+      <c r="C21" s="45" t="n"/>
+      <c r="D21" s="45" t="n"/>
+      <c r="E21" s="45" t="n"/>
+    </row>
+    <row r="22" s="24">
+      <c r="A22" s="45" t="n"/>
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="24">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="24">
-      <c r="A24" s="32" t="n"/>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B23" s="45" t="n"/>
+      <c r="C23" s="45" t="n"/>
+      <c r="D23" s="45" t="n"/>
+      <c r="E23" s="45" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="24">
+      <c r="A24" s="39" t="n"/>
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="24">
-      <c r="A25" s="33" t="n"/>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="24">
+      <c r="A25" s="48" t="n"/>
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>Biru muda: warna baris contoh, sudah dikosongkan dan tidak dipakai</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="24">
-      <c r="A26" s="34" t="n"/>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="24">
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="24">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+    </row>
+    <row r="27" s="24">
+      <c r="A27" s="45" t="n"/>
+      <c r="B27" s="45" t="n"/>
+      <c r="C27" s="45" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="45" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="24">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="24">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="B28" s="45" t="n"/>
+      <c r="C28" s="45" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="24">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="40" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="D29" s="40" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E29" s="35" t="inlineStr">
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1" s="24">
+    <row r="30" ht="30" customHeight="1" s="24">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>00</t>
@@ -1004,76 +1128,91 @@
       <c r="D31" s="28" t="n"/>
       <c r="E31" s="28" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="24">
-      <c r="A33" s="29" t="inlineStr">
+    <row r="32" s="24">
+      <c r="A32" s="45" t="n"/>
+      <c r="B32" s="45" t="n"/>
+      <c r="C32" s="45" t="n"/>
+      <c r="D32" s="45" t="n"/>
+      <c r="E32" s="45" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="24">
+      <c r="A33" s="47" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="24">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="B33" s="45" t="n"/>
+      <c r="C33" s="45" t="n"/>
+      <c r="D33" s="45" t="n"/>
+      <c r="E33" s="45" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="24">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="40" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr">
+      <c r="D34" s="40" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E34" s="45" t="n"/>
     </row>
     <row r="35" ht="27.75" customHeight="1" s="24">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="36" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="45" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="24">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="45" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="24">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="45" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1117,7 +1256,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1128,141 +1267,150 @@
     <col width="27" customWidth="1" style="23" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="24">
-      <c r="A1" s="38" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="24">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
       </c>
-      <c r="B1" s="38" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Status uji</t>
         </is>
       </c>
-      <c r="C1" s="38" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Severity defect</t>
         </is>
       </c>
-      <c r="D1" s="38" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>Status defect</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="24">
-      <c r="A2" s="30" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="24">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Fungsional</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>Belum</t>
         </is>
       </c>
-      <c r="C2" s="30" t="inlineStr">
+      <c r="C2" s="51" t="inlineStr">
         <is>
           <t>Kritis</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="51" t="inlineStr">
         <is>
           <t>Terbuka</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="24">
-      <c r="A3" s="30" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="24">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>Kinerja</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>Lolos</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>Tinggi</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="51" t="inlineStr">
         <is>
           <t>Diperbaiki</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="24">
-      <c r="A4" s="30" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="24">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Keamanan</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Gagal</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>Sedang</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Lolos retest</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="24">
-      <c r="A5" s="30" t="inlineStr">
+    <row r="5" ht="30" customHeight="1" s="24">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Backup dan restore</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Diblokir</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Rendah</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Diterima sebagai isu sisa</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="24">
-      <c r="A6" s="30" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="24">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="24">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="B6" s="52" t="n"/>
+      <c r="C6" s="52" t="n"/>
+      <c r="D6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="24">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Akses</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="24">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="24">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Dokumentasi</t>
         </is>
       </c>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1270,7 +1418,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1361,7 +1509,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1379,7 +1527,9 @@
     <col width="34" customWidth="1" style="23" min="3" max="3"/>
     <col width="30" customWidth="1" style="23" min="4" max="4"/>
     <col width="28" customWidth="1" style="23" min="5" max="6"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="10" customWidth="1" style="23" min="7" max="8"/>
+    <col width="13" customWidth="1" style="24" min="8" max="8"/>
     <col width="14" customWidth="1" style="23" min="9" max="9"/>
     <col width="12" customWidth="1" style="23" min="10" max="10"/>
     <col width="24" customWidth="1" style="23" min="11" max="11"/>
@@ -1395,7 +1545,7 @@
     <row r="2" ht="15" customHeight="1" s="24">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Kasus berstatus Gagal wajib punya Defect ID di sheet Defect. Rekomendasi SIAP mensyaratkan tidak ada kasus Gagal atau Belum. Kasus yang lolos retest diubah menjadi Lolos (USULAN).</t>
+          <t>Setiap kasus berstatus Gagal wajib punya Defect ID di sheet Defect. Rekomendasi SIAP mensyaratkan tidak ada kasus Gagal atau Belum. Ubah status kasus yang lolos retest menjadi Lolos (USULAN).</t>
         </is>
       </c>
     </row>
@@ -2574,9 +2724,10 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="23" min="1" max="2"/>
+    <col width="13" customWidth="1" style="24" min="2" max="2"/>
     <col width="40" customWidth="1" style="23" min="3" max="3"/>
-    <col width="10" customWidth="1" style="23" min="4" max="4"/>
-    <col width="12" customWidth="1" style="23" min="5" max="5"/>
+    <col width="12" customWidth="1" style="23" min="4" max="4"/>
+    <col width="14" customWidth="1" style="23" min="5" max="5"/>
     <col width="16" customWidth="1" style="23" min="6" max="6"/>
     <col width="18" customWidth="1" style="23" min="7" max="7"/>
     <col width="12" customWidth="1" style="23" min="8" max="8"/>
@@ -2593,7 +2744,7 @@
     <row r="2" ht="15" customHeight="1" s="24">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Defect Kritis atau Tinggi berstatus Terbuka atau Diperbaiki menahan UAT.</t>
+          <t>UAT tertahan selama masih ada defect Kritis atau Tinggi yang berstatus Terbuka atau Diperbaiki.</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3268,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -3300,6 +3451,6 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>